--- a/data/trans_orig/IP22D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>54898</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35750</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44648</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>65089</t>
+          <t>65503</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D2_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,06%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4855</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6482</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22,7%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>77,48%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2440</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4748</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>84,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,36%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3207</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4634</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>82,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -1971,74 +1971,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7250</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>66,45%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>65,94%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>6074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>7624</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>74,98%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>39,61%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10627</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13772</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>59,71%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>34,74%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>77,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10577</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4903</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15434</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>85,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10562</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>59,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7392</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13066</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>72,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -2653,82 +2653,82 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4676</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3512</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7173</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>59,4%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>47,32%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8564</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4897</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10935</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>70,91%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>40,55%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>7357</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>4870</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9141</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>72,51%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>90,1%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,31%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,47 +3565,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3077</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>40,39%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -3678,74 +3678,74 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>59,61%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2477</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>65,45%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>15,81%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>19700</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>13650</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>26319</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>55,44%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>19593</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>13434</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>28633</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>60,37%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>41920</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>41847</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -4247,72 +4247,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>26827</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>20418</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>33098</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>56,51%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>27179</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>17730</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>33095</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>37,38%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>54879</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>46581</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>65503</t>
+          <t>62442</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -4360,82 +4360,82 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>99621</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>99621</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>99621</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
